--- a/bqr/_triggered.xlsx
+++ b/bqr/_triggered.xlsx
@@ -566,450 +566,442 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>CABO</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>9.06</v>
+        <v>53.26</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>2.49</v>
+        <v>4.14</v>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>9.06</v>
+        <v>53.3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>8.880000000000001</v>
+        <v>46.46</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>9.039999999999999</v>
+        <v>48.91</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-0.22</v>
+        <v>-8.17</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+        <v>47.93</v>
+      </c>
+      <c r="K2" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="L2" s="1" t="n">
-        <v>7.7</v>
+        <v>45.27</v>
       </c>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="1" t="n">
-        <v>7.25</v>
+        <v>42.61</v>
       </c>
       <c r="O2" s="4" t="inlineStr"/>
       <c r="P2" s="1" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="Q2" s="5" t="b">
-        <v>1</v>
-      </c>
+        <v>36.42</v>
+      </c>
+      <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="1" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="S2" s="6" t="b">
-        <v>1</v>
-      </c>
+        <v>33.2</v>
+      </c>
+      <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="1" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="U2" s="7" t="b">
-        <v>1</v>
-      </c>
+        <v>30.27</v>
+      </c>
+      <c r="U2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>CABO</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>9.06</v>
+        <v>53.26</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>2.49</v>
+        <v>4.14</v>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>8.9</v>
+        <v>46.86</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>8.57</v>
+        <v>42.58</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>8.859999999999999</v>
+        <v>42.63</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-2.21</v>
+        <v>-19.96</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>47.93</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="L3" s="1" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
+        <v>45.27</v>
+      </c>
+      <c r="M3" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="N3" s="1" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="O3" s="4" t="inlineStr"/>
+        <v>42.61</v>
+      </c>
+      <c r="O3" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="P3" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="5" t="b">
-        <v>1</v>
-      </c>
+        <v>33.2</v>
+      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="1" t="n">
-        <v>8.52</v>
+        <v>30.27</v>
       </c>
       <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="1" t="n">
-        <v>8.06</v>
+        <v>27.6</v>
       </c>
       <c r="U3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>OWLT</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>9.06</v>
+        <v>6.16</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>2.49</v>
+        <v>4.3</v>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>9.109999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>8.56</v>
+        <v>5.51</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>8.69</v>
+        <v>5.63</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-4.08</v>
+        <v>-8.6</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>5.54</v>
+      </c>
+      <c r="K4" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="L4" s="1" t="n">
-        <v>7.7</v>
+        <v>5.24</v>
       </c>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="1" t="n">
-        <v>7.25</v>
+        <v>4.93</v>
       </c>
       <c r="O4" s="4" t="inlineStr"/>
       <c r="P4" s="1" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="Q4" s="5" t="b">
-        <v>1</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="1" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="S4" s="6" t="b">
-        <v>1</v>
-      </c>
+        <v>3.18</v>
+      </c>
+      <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="1" t="n">
-        <v>8.4</v>
+        <v>2.89</v>
       </c>
       <c r="U4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>9.06</v>
+        <v>40.17</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>8.449999999999999</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>7.82</v>
+        <v>36.01</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>7.9</v>
+        <v>37.67</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>-12.8</v>
+        <v>-6.22</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>8.15</v>
+        <v>36.15</v>
       </c>
       <c r="K5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>7.7</v>
+        <v>34.14</v>
       </c>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="1" t="n">
-        <v>7.25</v>
+        <v>32.14</v>
       </c>
       <c r="O5" s="4" t="inlineStr"/>
       <c r="P5" s="1" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="Q5" s="5" t="b">
-        <v>1</v>
-      </c>
+        <v>33.85</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr"/>
       <c r="R5" s="1" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="S5" s="6" t="b">
-        <v>1</v>
-      </c>
+        <v>32.14</v>
+      </c>
+      <c r="S5" s="6" t="inlineStr"/>
       <c r="T5" s="1" t="n">
-        <v>7.81</v>
+        <v>30.51</v>
       </c>
       <c r="U5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>WNC</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>9.06</v>
+        <v>13.25</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>7.9</v>
+        <v>11.94</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>7.89</v>
+        <v>11.5</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>8.43</v>
+        <v>12.64</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-6.95</v>
+        <v>-4.6</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>8.15</v>
+        <v>11.92</v>
       </c>
       <c r="K6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>7.7</v>
+        <v>11.26</v>
       </c>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="1" t="n">
-        <v>7.25</v>
+        <v>10.6</v>
       </c>
       <c r="O6" s="4" t="inlineStr"/>
       <c r="P6" s="1" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="Q6" s="5" t="b">
-        <v>1</v>
-      </c>
+        <v>7.82</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="1" t="n">
-        <v>7.52</v>
+        <v>7.34</v>
       </c>
       <c r="S6" s="6" t="inlineStr"/>
       <c r="T6" s="1" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="U6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CABO</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>53.26</v>
+        <v>9.06</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>4.14</v>
+        <v>2.49</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>53.3</v>
+        <v>9.06</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46.46</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>48.91</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-8.17</v>
+        <v>-0.22</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="K7" s="2" t="b">
-        <v>1</v>
-      </c>
+        <v>8.15</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="1" t="n">
-        <v>45.27</v>
+        <v>7.7</v>
       </c>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="1" t="n">
-        <v>42.61</v>
+        <v>7.25</v>
       </c>
       <c r="O7" s="4" t="inlineStr"/>
       <c r="P7" s="1" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="Q7" s="5" t="inlineStr"/>
+        <v>14.69</v>
+      </c>
+      <c r="Q7" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="R7" s="1" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="S7" s="6" t="inlineStr"/>
+        <v>13.9</v>
+      </c>
+      <c r="S7" s="6" t="b">
+        <v>1</v>
+      </c>
       <c r="T7" s="1" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
+        <v>13.14</v>
+      </c>
+      <c r="U7" s="7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CABO</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>53.26</v>
+        <v>9.06</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>4.14</v>
+        <v>2.49</v>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46.86</v>
+        <v>8.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42.58</v>
+        <v>8.57</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>42.63</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-19.96</v>
+        <v>-2.21</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="K8" s="2" t="b">
-        <v>1</v>
-      </c>
+        <v>8.15</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="1" t="n">
-        <v>45.27</v>
-      </c>
-      <c r="M8" s="3" t="b">
-        <v>1</v>
-      </c>
+        <v>7.7</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="1" t="n">
-        <v>42.61</v>
-      </c>
-      <c r="O8" s="4" t="b">
-        <v>1</v>
-      </c>
+        <v>7.25</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr"/>
       <c r="P8" s="1" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="Q8" s="5" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Q8" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="R8" s="1" t="n">
-        <v>30.27</v>
+        <v>8.52</v>
       </c>
       <c r="S8" s="6" t="inlineStr"/>
       <c r="T8" s="1" t="n">
-        <v>27.6</v>
+        <v>8.06</v>
       </c>
       <c r="U8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
@@ -1018,59 +1010,61 @@
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>16.6</v>
+        <v>9.06</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>15.84</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>14.92</v>
+        <v>8.56</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>15.19</v>
+        <v>8.69</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-8.49</v>
+        <v>-4.08</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="K9" s="2" t="b">
-        <v>1</v>
-      </c>
+        <v>8.15</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="1" t="n">
-        <v>14.11</v>
+        <v>7.7</v>
       </c>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="1" t="n">
-        <v>13.28</v>
+        <v>7.25</v>
       </c>
       <c r="O9" s="4" t="inlineStr"/>
       <c r="P9" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q9" s="5" t="inlineStr"/>
+        <v>9.390000000000001</v>
+      </c>
+      <c r="Q9" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="R9" s="1" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="S9" s="6" t="inlineStr"/>
+        <v>8.880000000000001</v>
+      </c>
+      <c r="S9" s="6" t="b">
+        <v>1</v>
+      </c>
       <c r="T9" s="1" t="n">
-        <v>12.54</v>
+        <v>8.4</v>
       </c>
       <c r="U9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>CULP</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
@@ -1079,59 +1073,63 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>3.15</v>
+        <v>9.06</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>3.22</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>3.15</v>
+        <v>7.82</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>3.19</v>
+        <v>7.9</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>1.27</v>
+        <v>-12.8</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>8.15</v>
+      </c>
+      <c r="K10" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="L10" s="1" t="n">
-        <v>2.68</v>
+        <v>7.7</v>
       </c>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="1" t="n">
-        <v>2.52</v>
+        <v>7.25</v>
       </c>
       <c r="O10" s="4" t="inlineStr"/>
       <c r="P10" s="1" t="n">
-        <v>3.16</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="S10" s="6" t="inlineStr"/>
+        <v>8.25</v>
+      </c>
+      <c r="S10" s="6" t="b">
+        <v>1</v>
+      </c>
       <c r="T10" s="1" t="n">
-        <v>2.9</v>
+        <v>7.81</v>
       </c>
       <c r="U10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>FOXF</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
@@ -1140,59 +1138,61 @@
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>17.79</v>
+        <v>9.06</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>17.2</v>
+        <v>7.9</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>15.68</v>
+        <v>7.89</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>16.95</v>
+        <v>8.43</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>-4.72</v>
+        <v>-6.95</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>16.01</v>
+        <v>8.15</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>15.12</v>
+        <v>7.7</v>
       </c>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="1" t="n">
-        <v>14.23</v>
+        <v>7.25</v>
       </c>
       <c r="O11" s="4" t="inlineStr"/>
       <c r="P11" s="1" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Q11" s="5" t="inlineStr"/>
+        <v>7.95</v>
+      </c>
+      <c r="Q11" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="R11" s="1" t="n">
-        <v>13.91</v>
+        <v>7.52</v>
       </c>
       <c r="S11" s="6" t="inlineStr"/>
       <c r="T11" s="1" t="n">
-        <v>13.08</v>
+        <v>7.12</v>
       </c>
       <c r="U11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>KRO</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -1201,59 +1201,59 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>6.99</v>
+        <v>16.6</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>6.52</v>
+        <v>15.84</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>6.26</v>
+        <v>14.92</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>6.56</v>
+        <v>15.19</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-6.15</v>
+        <v>-8.49</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>6.29</v>
+        <v>14.94</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>5.94</v>
+        <v>14.11</v>
       </c>
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="1" t="n">
-        <v>5.59</v>
+        <v>13.28</v>
       </c>
       <c r="O12" s="4" t="inlineStr"/>
       <c r="P12" s="1" t="n">
-        <v>5.45</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="1" t="n">
-        <v>5.04</v>
+        <v>13.25</v>
       </c>
       <c r="S12" s="6" t="inlineStr"/>
       <c r="T12" s="1" t="n">
-        <v>4.66</v>
+        <v>12.54</v>
       </c>
       <c r="U12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>KRO</t>
+          <t>CULP</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
@@ -1262,122 +1262,120 @@
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>6.99</v>
+        <v>3.15</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>6.04</v>
+        <v>3.22</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>5.82</v>
+        <v>3.15</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>5.84</v>
+        <v>3.19</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>-16.45</v>
+        <v>1.27</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="K13" s="2" t="b">
-        <v>1</v>
-      </c>
+        <v>2.84</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="1" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="M13" s="3" t="b">
-        <v>1</v>
-      </c>
+        <v>2.68</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="1" t="n">
-        <v>5.59</v>
+        <v>2.52</v>
       </c>
       <c r="O13" s="4" t="inlineStr"/>
       <c r="P13" s="1" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="Q13" s="5" t="inlineStr"/>
+        <v>3.16</v>
+      </c>
+      <c r="Q13" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="R13" s="1" t="n">
-        <v>5.01</v>
+        <v>3.03</v>
       </c>
       <c r="S13" s="6" t="inlineStr"/>
       <c r="T13" s="1" t="n">
-        <v>4.64</v>
+        <v>2.9</v>
       </c>
       <c r="U13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>OWLT</t>
+          <t>FOXF</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>6.16</v>
+        <v>17.79</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>5.85</v>
+        <v>17.2</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>5.51</v>
+        <v>15.68</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>5.63</v>
+        <v>16.95</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>-8.6</v>
+        <v>-4.72</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>5.54</v>
+        <v>16.01</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>5.24</v>
+        <v>15.12</v>
       </c>
       <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="1" t="n">
-        <v>4.93</v>
+        <v>14.23</v>
       </c>
       <c r="O14" s="4" t="inlineStr"/>
       <c r="P14" s="1" t="n">
-        <v>3.5</v>
+        <v>14.8</v>
       </c>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="1" t="n">
-        <v>3.18</v>
+        <v>13.91</v>
       </c>
       <c r="S14" s="6" t="inlineStr"/>
       <c r="T14" s="1" t="n">
-        <v>2.89</v>
+        <v>13.08</v>
       </c>
       <c r="U14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>KRO</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
@@ -1386,59 +1384,59 @@
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>13.27</v>
+        <v>6.99</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>12.16</v>
+        <v>6.52</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>11.93</v>
+        <v>6.26</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>11.94</v>
+        <v>6.56</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-10.02</v>
+        <v>-6.15</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>11.94</v>
+        <v>6.29</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>11.28</v>
+        <v>5.94</v>
       </c>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="1" t="n">
-        <v>10.62</v>
+        <v>5.59</v>
       </c>
       <c r="O15" s="4" t="inlineStr"/>
       <c r="P15" s="1" t="n">
-        <v>9.199999999999999</v>
+        <v>5.45</v>
       </c>
       <c r="Q15" s="5" t="inlineStr"/>
       <c r="R15" s="1" t="n">
-        <v>8.460000000000001</v>
+        <v>5.04</v>
       </c>
       <c r="S15" s="6" t="inlineStr"/>
       <c r="T15" s="1" t="n">
-        <v>7.77</v>
+        <v>4.66</v>
       </c>
       <c r="U15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>KRO</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
@@ -1447,59 +1445,61 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>12.18</v>
+        <v>6.99</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>4.52</v>
+        <v>3.5</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>12.36</v>
+        <v>6.04</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>10.53</v>
+        <v>5.82</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>10.81</v>
+        <v>5.84</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-11.25</v>
+        <v>-16.45</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>10.96</v>
+        <v>6.29</v>
       </c>
       <c r="K16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr"/>
+        <v>5.94</v>
+      </c>
+      <c r="M16" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="N16" s="1" t="n">
-        <v>9.74</v>
+        <v>5.59</v>
       </c>
       <c r="O16" s="4" t="inlineStr"/>
       <c r="P16" s="1" t="n">
-        <v>5.79</v>
+        <v>5.42</v>
       </c>
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="1" t="n">
-        <v>5.23</v>
+        <v>5.01</v>
       </c>
       <c r="S16" s="6" t="inlineStr"/>
       <c r="T16" s="1" t="n">
-        <v>4.73</v>
+        <v>4.64</v>
       </c>
       <c r="U16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
@@ -1508,56 +1508,52 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>12.18</v>
+        <v>13.27</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>4.52</v>
+        <v>3.78</v>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F17" s="1" t="n">
-        <v>11.05</v>
+        <v>12.16</v>
       </c>
       <c r="G17" s="1" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>-10.02</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="K17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="1" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="1" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>-20.94</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="K17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="M17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="O17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>6.88</v>
       </c>
       <c r="Q17" s="5" t="inlineStr"/>
       <c r="R17" s="1" t="n">
-        <v>6.22</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="S17" s="6" t="inlineStr"/>
       <c r="T17" s="1" t="n">
-        <v>5.62</v>
+        <v>7.77</v>
       </c>
       <c r="U17" s="7" t="inlineStr"/>
     </row>
@@ -1580,20 +1576,20 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>10.07</v>
+        <v>12.36</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>9.99</v>
+        <v>10.53</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>10.43</v>
+        <v>10.81</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-14.37</v>
+        <v>-11.25</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>10.96</v>
@@ -1604,23 +1600,21 @@
       <c r="L18" s="1" t="n">
         <v>10.35</v>
       </c>
-      <c r="M18" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="1" t="n">
         <v>9.74</v>
       </c>
       <c r="O18" s="4" t="inlineStr"/>
       <c r="P18" s="1" t="n">
-        <v>6.85</v>
+        <v>5.79</v>
       </c>
       <c r="Q18" s="5" t="inlineStr"/>
       <c r="R18" s="1" t="n">
-        <v>6.19</v>
+        <v>5.23</v>
       </c>
       <c r="S18" s="6" t="inlineStr"/>
       <c r="T18" s="1" t="n">
-        <v>5.6</v>
+        <v>4.73</v>
       </c>
       <c r="U18" s="7" t="inlineStr"/>
     </row>
@@ -1643,20 +1637,20 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>9.56</v>
+        <v>11.05</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>8.94</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>9</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-26.11</v>
+        <v>-20.94</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>10.96</v>
@@ -1677,139 +1671,145 @@
         <v>1</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="Q19" s="5" t="b">
-        <v>1</v>
-      </c>
+        <v>6.88</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr"/>
       <c r="R19" s="1" t="n">
-        <v>8.140000000000001</v>
+        <v>6.22</v>
       </c>
       <c r="S19" s="6" t="inlineStr"/>
       <c r="T19" s="1" t="n">
-        <v>7.36</v>
+        <v>5.62</v>
       </c>
       <c r="U19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>WHR</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>40.17</v>
+        <v>12.18</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>2.32</v>
+        <v>4.52</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>37</v>
+        <v>10.07</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>36.01</v>
+        <v>9.99</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>37.67</v>
+        <v>10.43</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-6.22</v>
+        <v>-14.37</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>36.15</v>
+        <v>10.96</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="M20" s="3" t="inlineStr"/>
+        <v>10.35</v>
+      </c>
+      <c r="M20" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="N20" s="1" t="n">
-        <v>32.14</v>
+        <v>9.74</v>
       </c>
       <c r="O20" s="4" t="inlineStr"/>
       <c r="P20" s="1" t="n">
-        <v>33.85</v>
+        <v>6.85</v>
       </c>
       <c r="Q20" s="5" t="inlineStr"/>
       <c r="R20" s="1" t="n">
-        <v>32.14</v>
+        <v>6.19</v>
       </c>
       <c r="S20" s="6" t="inlineStr"/>
       <c r="T20" s="1" t="n">
-        <v>30.51</v>
+        <v>5.6</v>
       </c>
       <c r="U20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>WNC</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>13.25</v>
+        <v>12.18</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>2.83</v>
+        <v>4.52</v>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>11.94</v>
+        <v>9.56</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>11.5</v>
+        <v>8.94</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>12.64</v>
+        <v>9</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-4.6</v>
+        <v>-26.11</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>11.92</v>
+        <v>10.96</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
+        <v>10.35</v>
+      </c>
+      <c r="M21" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="N21" s="1" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="O21" s="4" t="inlineStr"/>
+        <v>9.74</v>
+      </c>
+      <c r="O21" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="P21" s="1" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="Q21" s="5" t="inlineStr"/>
+        <v>9.01</v>
+      </c>
+      <c r="Q21" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="R21" s="1" t="n">
-        <v>7.34</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S21" s="6" t="inlineStr"/>
       <c r="T21" s="1" t="n">
-        <v>6.89</v>
+        <v>7.36</v>
       </c>
       <c r="U21" s="7" t="inlineStr"/>
     </row>
